--- a/División/MSPS_División.xlsx
+++ b/División/MSPS_División.xlsx
@@ -431,13 +431,13 @@
         <v>45.54036027117925</v>
       </c>
       <c r="C2" s="2">
-        <v>114.4546694464065</v>
+        <v>114.4526276680616</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>52.12306881308086</v>
+        <v>52.12213897986663</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -454,7 +454,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="2">
-        <v>20.71338431637632</v>
+        <v>20.71338431637633</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -465,7 +465,7 @@
         <v>14.79738269611555</v>
       </c>
       <c r="C4" s="2">
-        <v>119.1218955095634</v>
+        <v>119.1218955095635</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
@@ -482,7 +482,7 @@
         <v>20.8258977826234</v>
       </c>
       <c r="C5" s="2">
-        <v>112.8741680619669</v>
+        <v>112.8741680619668</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>6</v>
